--- a/BOM MENU.xlsx
+++ b/BOM MENU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Bujang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01C1F40F-7318-4ABB-831F-C8B05AB98A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C89B953-40A2-42E5-BF76-3273BE202914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3C390418-F7AC-4F51-8895-39683B59FCF4}"/>
   </bookViews>

--- a/BOM MENU.xlsx
+++ b/BOM MENU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Bujang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C89B953-40A2-42E5-BF76-3273BE202914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E90A38A-00B5-423B-A712-49B919B8BDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3C390418-F7AC-4F51-8895-39683B59FCF4}"/>
   </bookViews>
